--- a/sup_tables/sup_table_s15_sex_bias.xlsx
+++ b/sup_tables/sup_table_s15_sex_bias.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">CancerType</t>
   </si>
@@ -38,21 +38,33 @@
     <t xml:space="preserve">p.adj</t>
   </si>
   <si>
+    <t xml:space="preserve">Pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_ID12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_ID3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Esophagus</t>
   </si>
   <si>
     <t xml:space="preserve">InsDel1a</t>
   </si>
   <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel3b</t>
-  </si>
-  <si>
     <t xml:space="preserve">Liver</t>
   </si>
   <si>
@@ -65,12 +77,12 @@
     <t xml:space="preserve">C_ID1</t>
   </si>
   <si>
+    <t xml:space="preserve">C_ID5</t>
+  </si>
+  <si>
     <t xml:space="preserve">C_ID8</t>
   </si>
   <si>
-    <t xml:space="preserve">C_ID3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Other</t>
   </si>
   <si>
@@ -80,19 +92,37 @@
     <t xml:space="preserve">Lymphoid</t>
   </si>
   <si>
+    <t xml:space="preserve">InsDel19b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biliary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bone.SoftTissue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel_B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel_A_alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head</t>
+  </si>
+  <si>
     <t xml:space="preserve">InsDel1c</t>
   </si>
   <si>
-    <t xml:space="preserve">InsDel19b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_ID5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biliary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bone.SoftTissue</t>
+    <t xml:space="preserve">Skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_A</t>
   </si>
   <si>
     <t xml:space="preserve">ID_B</t>
@@ -104,106 +134,88 @@
     <t xml:space="preserve">C_ID2</t>
   </si>
   <si>
-    <t xml:space="preserve">Colon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID_A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kidney</t>
   </si>
   <si>
+    <t xml:space="preserve">C_ID6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_ID4</t>
+  </si>
+  <si>
     <t xml:space="preserve">C_ID9</t>
   </si>
   <si>
-    <t xml:space="preserve">Skin</t>
-  </si>
-  <si>
     <t xml:space="preserve">C_ID13</t>
   </si>
   <si>
+    <t xml:space="preserve">ID_N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel_N_beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel2a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thymus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_D</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stomach</t>
   </si>
   <si>
-    <t xml:space="preserve">InsDel_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel_A_alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel2a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel_N_beta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID_N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thymus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Myeloid</t>
   </si>
   <si>
-    <t xml:space="preserve">Pancreas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bladder</t>
   </si>
   <si>
-    <t xml:space="preserve">C_ID4</t>
-  </si>
-  <si>
     <t xml:space="preserve">C_ID10</t>
   </si>
   <si>
-    <t xml:space="preserve">ID_D</t>
+    <t xml:space="preserve">C_ID7</t>
   </si>
   <si>
     <t xml:space="preserve">C_ID14</t>
   </si>
   <si>
+    <t xml:space="preserve">InsDel_D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel19a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel2c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InsDel18</t>
+  </si>
+  <si>
     <t xml:space="preserve">C_ID18</t>
   </si>
   <si>
-    <t xml:space="preserve">C_ID7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel_D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_ID6</t>
-  </si>
-  <si>
     <t xml:space="preserve">InsDel5b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InsDel6</t>
   </si>
 </sst>
 </file>
@@ -569,102 +581,102 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00133630120645587</v>
+        <v>0.000140647851048746</v>
       </c>
       <c r="G2" t="n">
-        <v>3.84549582695721</v>
+        <v>8.05238671053058</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0614698554969702</v>
+        <v>0.0143460808069721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000751311114503039</v>
+        <v>0.000140647851048746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.367028213250231</v>
+        <v>8.05238671053058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0614698554969702</v>
+        <v>0.0143460808069721</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00385330359155569</v>
+        <v>0.000615686531281531</v>
       </c>
       <c r="G4" t="n">
-        <v>0.48080075295598</v>
+        <v>0.348269388711341</v>
       </c>
       <c r="H4" t="n">
-        <v>0.118167976807708</v>
+        <v>0.0314000130953581</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00798437046406813</v>
+        <v>0.00159446406825573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.270665346691066</v>
+        <v>0.376756829017376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.183640520673567</v>
+        <v>0.0813176674810422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -673,76 +685,76 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00409990437729872</v>
+        <v>0.00310220925215463</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22282681374888</v>
+        <v>3.39615792889441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.187632705905601</v>
+        <v>0.105475114573258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00798437046406813</v>
+        <v>0.00800742853641258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.270665346691066</v>
+        <v>0.504628232022728</v>
       </c>
       <c r="H7" t="n">
-        <v>0.187632705905601</v>
+        <v>0.163351542142817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00281135498423805</v>
+        <v>0.00798437046406813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.397050596572556</v>
+        <v>0.270665346691066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.187632705905601</v>
+        <v>0.163351542142817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
@@ -751,76 +763,76 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00791973762816828</v>
+        <v>0.00842512122669239</v>
       </c>
       <c r="G9" t="n">
-        <v>0.424345752577453</v>
+        <v>2.96007974621198</v>
       </c>
       <c r="H9" t="n">
-        <v>0.187632705905601</v>
+        <v>0.182052754779452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
         <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01056037920811</v>
+        <v>0.00892415464605159</v>
       </c>
       <c r="G10" t="n">
-        <v>2.63052373514104</v>
+        <v>0.525679482696508</v>
       </c>
       <c r="H10" t="n">
-        <v>0.194310977429223</v>
+        <v>0.182052754779452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0128249613101494</v>
+        <v>0.00798437046406813</v>
       </c>
       <c r="G11" t="n">
-        <v>0.448406880788594</v>
+        <v>0.270665346691066</v>
       </c>
       <c r="H11" t="n">
-        <v>0.196649406755625</v>
+        <v>0.182052754779452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -829,97 +841,97 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>0.023995483033655</v>
+        <v>0.0174034159687728</v>
       </c>
       <c r="G12" t="n">
-        <v>0.573259039537162</v>
+        <v>0.460588020817428</v>
       </c>
       <c r="H12" t="n">
-        <v>0.451115081032714</v>
+        <v>0.295858071469138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0370510924253743</v>
+        <v>0.0223853801026741</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8941689032524</v>
+        <v>2.01977456450611</v>
       </c>
       <c r="H13" t="n">
-        <v>0.580467114664197</v>
+        <v>0.326186967210394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>0.133069977376094</v>
+        <v>0.0201590111059958</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0202607439352</v>
+        <v>0.473093948212986</v>
       </c>
       <c r="H14" t="n">
-        <v>0.689434029027634</v>
+        <v>0.342703188801929</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0703814769214052</v>
+        <v>0.0859851877684654</v>
       </c>
       <c r="G15" t="n">
-        <v>0.531025881791579</v>
+        <v>2.23355596907625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="16">
@@ -933,19 +945,19 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0755235763452978</v>
+        <v>0.0703814769214052</v>
       </c>
       <c r="G16" t="n">
-        <v>2.31936182788185</v>
+        <v>0.531025881791579</v>
       </c>
       <c r="H16" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="17">
@@ -953,371 +965,371 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F17" t="n">
-        <v>0.146427825650744</v>
+        <v>0.0713276444129236</v>
       </c>
       <c r="G17" t="n">
-        <v>0.636587649638136</v>
+        <v>0.521663685908353</v>
       </c>
       <c r="H17" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>0.109051384776108</v>
+        <v>0.0797627103217908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.527163852615347</v>
+        <v>2.37595189094849</v>
       </c>
       <c r="H18" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0797627103217908</v>
+        <v>0.0913083090428636</v>
       </c>
       <c r="G19" t="n">
-        <v>2.37595189094849</v>
+        <v>0.653511921412859</v>
       </c>
       <c r="H19" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>0.134040021272604</v>
+        <v>0.0942905680549751</v>
       </c>
       <c r="G20" t="n">
-        <v>0.60013522735527</v>
+        <v>1.50612609378294</v>
       </c>
       <c r="H20" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0691295750246238</v>
+        <v>0.050591490053032</v>
       </c>
       <c r="G21" t="n">
-        <v>0.637182372875605</v>
+        <v>2.03307503069615</v>
       </c>
       <c r="H21" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0942905680549751</v>
+        <v>0.0970435555710256</v>
       </c>
       <c r="G22" t="n">
-        <v>1.50612609378294</v>
+        <v>0.623331849548772</v>
       </c>
       <c r="H22" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F23" t="n">
-        <v>0.127822839014168</v>
+        <v>0.0634463963170974</v>
       </c>
       <c r="G23" t="n">
-        <v>1.59963702218891</v>
+        <v>1.59258537893122</v>
       </c>
       <c r="H23" t="n">
-        <v>0.689434029027634</v>
+        <v>0.659896177882974</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="F24" t="n">
-        <v>0.138094019750899</v>
+        <v>0.0520003257580991</v>
       </c>
       <c r="G24" t="n">
-        <v>1.48104732962125</v>
+        <v>0.502619605176981</v>
       </c>
       <c r="H24" t="n">
-        <v>0.689434029027634</v>
+        <v>0.663004153415763</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0970435555710256</v>
+        <v>0.0703814769214052</v>
       </c>
       <c r="G25" t="n">
-        <v>0.623331849548772</v>
+        <v>0.531025881791579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.689434029027634</v>
+        <v>0.705487426831914</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="F26" t="n">
-        <v>0.139188197442656</v>
+        <v>0.0760819774034417</v>
       </c>
       <c r="G26" t="n">
-        <v>1.48382200963099</v>
+        <v>2.06004969343999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.689434029027634</v>
+        <v>0.705487426831914</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F27" t="n">
-        <v>0.146688091282475</v>
+        <v>0.0691295750246238</v>
       </c>
       <c r="G27" t="n">
-        <v>0.285096100346663</v>
+        <v>0.637182372875605</v>
       </c>
       <c r="H27" t="n">
-        <v>0.689434029027634</v>
+        <v>0.705487426831914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0703814769214052</v>
+        <v>0.133734360085819</v>
       </c>
       <c r="G28" t="n">
-        <v>0.531025881791579</v>
+        <v>2.18158720729222</v>
       </c>
       <c r="H28" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.069845610524094</v>
+        <v>0.163144997379589</v>
       </c>
       <c r="G29" t="n">
-        <v>0.471846781855324</v>
+        <v>0.473282626295156</v>
       </c>
       <c r="H29" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0797627103217908</v>
+        <v>0.134040021272604</v>
       </c>
       <c r="G30" t="n">
-        <v>2.37595189094849</v>
+        <v>0.60013522735527</v>
       </c>
       <c r="H30" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
@@ -1329,65 +1341,65 @@
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0913083090428636</v>
+        <v>0.0942905680549751</v>
       </c>
       <c r="G31" t="n">
-        <v>0.653511921412859</v>
+        <v>1.50612609378294</v>
       </c>
       <c r="H31" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0942905680549751</v>
+        <v>0.170300324489083</v>
       </c>
       <c r="G32" t="n">
-        <v>1.50612609378294</v>
+        <v>0.479068408625465</v>
       </c>
       <c r="H32" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0970435555710256</v>
+        <v>0.143697099682524</v>
       </c>
       <c r="G33" t="n">
-        <v>0.623331849548772</v>
+        <v>0.495104137637538</v>
       </c>
       <c r="H33" t="n">
-        <v>0.744000592711196</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="34">
@@ -1395,316 +1407,316 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>0.133069977376094</v>
+        <v>0.12909179795656</v>
       </c>
       <c r="G34" t="n">
-        <v>2.0202607439352</v>
+        <v>1.61712094828828</v>
       </c>
       <c r="H34" t="n">
-        <v>0.765152369912542</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="F35" t="n">
-        <v>0.109051384776108</v>
+        <v>0.172997905885507</v>
       </c>
       <c r="G35" t="n">
-        <v>0.527163852615347</v>
+        <v>0.48531240164121</v>
       </c>
       <c r="H35" t="n">
-        <v>0.765152369912542</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.13163883659196</v>
+        <v>0.178102681497339</v>
       </c>
       <c r="G36" t="n">
-        <v>0.568797970663849</v>
+        <v>0.6774883338098</v>
       </c>
       <c r="H36" t="n">
-        <v>0.765152369912542</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E37" t="n">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="F37" t="n">
-        <v>0.127822839014168</v>
+        <v>0.120994316457053</v>
       </c>
       <c r="G37" t="n">
-        <v>1.59963702218891</v>
+        <v>1.78098790421472</v>
       </c>
       <c r="H37" t="n">
-        <v>0.765152369912542</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
-        <v>0.144146728573683</v>
+        <v>0.138094019750899</v>
       </c>
       <c r="G38" t="n">
-        <v>0.451798407580626</v>
+        <v>1.48104732962125</v>
       </c>
       <c r="H38" t="n">
-        <v>0.780088178163461</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E39" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>0.187085213400089</v>
+        <v>0.0970435555710256</v>
       </c>
       <c r="G39" t="n">
-        <v>1.70090084009565</v>
+        <v>0.623331849548772</v>
       </c>
       <c r="H39" t="n">
-        <v>0.780525094068632</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n">
-        <v>0.190527506643327</v>
+        <v>0.139188197442656</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7423101754118</v>
+        <v>1.48382200963099</v>
       </c>
       <c r="H40" t="n">
-        <v>0.780525094068632</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="F41" t="n">
-        <v>0.195131273517158</v>
+        <v>0.177071458130733</v>
       </c>
       <c r="G41" t="n">
-        <v>1.52633852222875</v>
+        <v>1.50814816575158</v>
       </c>
       <c r="H41" t="n">
-        <v>0.780525094068632</v>
+        <v>0.726658940509143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E42" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="F42" t="n">
-        <v>0.175489840382838</v>
+        <v>0.126568251105607</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42783814040654</v>
+        <v>1.86187276180306</v>
       </c>
       <c r="H42" t="n">
-        <v>0.780525094068632</v>
+        <v>0.732855208380874</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>0.171178439777637</v>
+        <v>0.131762180957529</v>
       </c>
       <c r="G43" t="n">
-        <v>1.42109078450039</v>
+        <v>0.549503396427544</v>
       </c>
       <c r="H43" t="n">
-        <v>0.780525094068632</v>
+        <v>0.732855208380874</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F44" t="n">
-        <v>0.167764359524002</v>
+        <v>0.143697099682524</v>
       </c>
       <c r="G44" t="n">
-        <v>1.54746091568663</v>
+        <v>0.495104137637538</v>
       </c>
       <c r="H44" t="n">
-        <v>0.780525094068632</v>
+        <v>0.732855208380874</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E45" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="F45" t="n">
-        <v>0.177071458130733</v>
+        <v>0.12909179795656</v>
       </c>
       <c r="G45" t="n">
-        <v>1.50814816575158</v>
+        <v>1.61712094828828</v>
       </c>
       <c r="H45" t="n">
-        <v>0.792605574489949</v>
+        <v>0.732855208380874</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
@@ -1713,622 +1725,622 @@
         <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="F46" t="n">
-        <v>0.189639985145875</v>
+        <v>0.142510908201225</v>
       </c>
       <c r="G46" t="n">
-        <v>1.98525360040255</v>
+        <v>0.720581767990177</v>
       </c>
       <c r="H46" t="n">
-        <v>0.802376665973795</v>
+        <v>0.732855208380874</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="F47" t="n">
-        <v>0.196326205504227</v>
+        <v>0.170300324489083</v>
       </c>
       <c r="G47" t="n">
-        <v>0.388613506933247</v>
+        <v>0.479068408625465</v>
       </c>
       <c r="H47" t="n">
-        <v>0.802376665973795</v>
+        <v>0.74583182162706</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="F48" t="n">
-        <v>0.252096205722342</v>
+        <v>0.173034629869801</v>
       </c>
       <c r="G48" t="n">
-        <v>0.698901742218941</v>
+        <v>1.81189615674989</v>
       </c>
       <c r="H48" t="n">
-        <v>0.82551219046425</v>
+        <v>0.74583182162706</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
         <v>26</v>
       </c>
-      <c r="B49" t="s">
-        <v>34</v>
-      </c>
       <c r="C49" t="s">
         <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F49" t="n">
-        <v>0.266996292293019</v>
+        <v>0.175489840382838</v>
       </c>
       <c r="G49" t="n">
-        <v>1.37259052397131</v>
+        <v>1.42783814040654</v>
       </c>
       <c r="H49" t="n">
-        <v>0.82551219046425</v>
+        <v>0.74583182162706</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="n">
         <v>26</v>
       </c>
-      <c r="B50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" t="n">
-        <v>21</v>
-      </c>
       <c r="E50" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F50" t="n">
-        <v>0.27471311704447</v>
+        <v>0.167764359524002</v>
       </c>
       <c r="G50" t="n">
-        <v>1.53339777555667</v>
+        <v>1.54746091568663</v>
       </c>
       <c r="H50" t="n">
-        <v>0.82551219046425</v>
+        <v>0.74583182162706</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E51" t="n">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="F51" t="n">
-        <v>0.281025426541021</v>
+        <v>0.1986742278101</v>
       </c>
       <c r="G51" t="n">
-        <v>0.781142436106012</v>
+        <v>1.88020234353029</v>
       </c>
       <c r="H51" t="n">
-        <v>0.82551219046425</v>
+        <v>0.750547082838155</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F52" t="n">
-        <v>0.245998151183368</v>
+        <v>0.196326205504227</v>
       </c>
       <c r="G52" t="n">
-        <v>1.43293546078285</v>
+        <v>0.388613506933247</v>
       </c>
       <c r="H52" t="n">
-        <v>0.82551219046425</v>
+        <v>0.750547082838155</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="n">
         <v>8</v>
       </c>
-      <c r="B53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" t="n">
-        <v>26</v>
-      </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F53" t="n">
-        <v>0.217387804613155</v>
+        <v>0.229671436635334</v>
       </c>
       <c r="G53" t="n">
-        <v>0.480350022074456</v>
+        <v>0.503914745105632</v>
       </c>
       <c r="H53" t="n">
-        <v>0.82551219046425</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
-        <v>0.235134298411267</v>
+        <v>0.252096205722342</v>
       </c>
       <c r="G54" t="n">
-        <v>0.50321444727453</v>
+        <v>0.698901742218941</v>
       </c>
       <c r="H54" t="n">
-        <v>0.82551219046425</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F55" t="n">
-        <v>0.237228079336741</v>
+        <v>0.27471311704447</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84776965457126</v>
+        <v>1.53339777555667</v>
       </c>
       <c r="H55" t="n">
-        <v>0.82551219046425</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E56" t="n">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="F56" t="n">
-        <v>0.266702726065325</v>
+        <v>0.282642017764431</v>
       </c>
       <c r="G56" t="n">
-        <v>0.561018776785422</v>
+        <v>0.661461097809395</v>
       </c>
       <c r="H56" t="n">
-        <v>0.82551219046425</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F57" t="n">
-        <v>0.343781105140299</v>
+        <v>0.237228079336741</v>
       </c>
       <c r="G57" t="n">
-        <v>0.584229780453583</v>
+        <v>1.84776965457126</v>
       </c>
       <c r="H57" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="F58" t="n">
-        <v>0.367935183228812</v>
+        <v>0.231388372436585</v>
       </c>
       <c r="G58" t="n">
-        <v>0.613078683079382</v>
+        <v>0.631033666030929</v>
       </c>
       <c r="H58" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="E59" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F59" t="n">
-        <v>0.33543230933371</v>
+        <v>0.283684123311514</v>
       </c>
       <c r="G59" t="n">
-        <v>0.535131224047242</v>
+        <v>1.4520388992431</v>
       </c>
       <c r="H59" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F60" t="n">
-        <v>0.371491397342271</v>
+        <v>0.278055824180454</v>
       </c>
       <c r="G60" t="n">
-        <v>0.60295244347598</v>
+        <v>1.67174349422142</v>
       </c>
       <c r="H60" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F61" t="n">
-        <v>0.298372544552273</v>
+        <v>0.256294234330313</v>
       </c>
       <c r="G61" t="n">
-        <v>0.583828821356584</v>
+        <v>1.58538658668626</v>
       </c>
       <c r="H61" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
-        <v>0.328742310242566</v>
+        <v>0.264810124313741</v>
       </c>
       <c r="G62" t="n">
-        <v>0.577378436852331</v>
+        <v>0.417405201243115</v>
       </c>
       <c r="H62" t="n">
-        <v>0.831433127385083</v>
+        <v>0.782048123723634</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
         <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F63" t="n">
-        <v>0.348694622061562</v>
+        <v>0.298372544552273</v>
       </c>
       <c r="G63" t="n">
-        <v>1.36756598754102</v>
+        <v>0.583828821356584</v>
       </c>
       <c r="H63" t="n">
-        <v>0.831433127385083</v>
+        <v>0.800894724850837</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C64" t="s">
         <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E64" t="n">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="F64" t="n">
-        <v>0.360036922887737</v>
+        <v>0.330798984350319</v>
       </c>
       <c r="G64" t="n">
-        <v>0.719058302138559</v>
+        <v>1.32136851193317</v>
       </c>
       <c r="H64" t="n">
-        <v>0.831433127385083</v>
+        <v>0.803368961993632</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E65" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="F65" t="n">
-        <v>0.349942905872178</v>
+        <v>0.326990727525985</v>
       </c>
       <c r="G65" t="n">
-        <v>0.671962952762743</v>
+        <v>0.73437588059406</v>
       </c>
       <c r="H65" t="n">
-        <v>0.831433127385083</v>
+        <v>0.803368961993632</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>0.33959255376214</v>
+        <v>0.328742310242566</v>
       </c>
       <c r="G66" t="n">
-        <v>1.47007645723898</v>
+        <v>0.577378436852331</v>
       </c>
       <c r="H66" t="n">
-        <v>0.831433127385083</v>
+        <v>0.803368961993632</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
         <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>0.39022905751721</v>
+        <v>0.319789668184136</v>
       </c>
       <c r="G67" t="n">
-        <v>1.50080804067479</v>
+        <v>1.62030465604548</v>
       </c>
       <c r="H67" t="n">
-        <v>0.83367116833222</v>
+        <v>0.803368961993632</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C68" t="s">
         <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E68" t="n">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>0.388595830158031</v>
+        <v>0.389119028413306</v>
       </c>
       <c r="G68" t="n">
-        <v>1.55352427730225</v>
+        <v>1.48510758502867</v>
       </c>
       <c r="H68" t="n">
-        <v>0.83367116833222</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F69" t="n">
-        <v>0.221131765677778</v>
+        <v>0.374819560353568</v>
       </c>
       <c r="G69" t="n">
-        <v>0.518988544656163</v>
+        <v>0.615959402965158</v>
       </c>
       <c r="H69" t="n">
-        <v>0.839422434576162</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -2337,27 +2349,27 @@
         <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>0.235134298411267</v>
+        <v>0.363749970274798</v>
       </c>
       <c r="G70" t="n">
-        <v>0.50321444727453</v>
+        <v>0.62352092058455</v>
       </c>
       <c r="H70" t="n">
-        <v>0.839422434576162</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C71" t="s">
         <v>10</v>
@@ -2366,50 +2378,50 @@
         <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="F71" t="n">
-        <v>0.237228079336741</v>
+        <v>0.497764865490098</v>
       </c>
       <c r="G71" t="n">
-        <v>1.84776965457126</v>
+        <v>1.40428524356967</v>
       </c>
       <c r="H71" t="n">
-        <v>0.839422434576162</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C72" t="s">
         <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="F72" t="n">
-        <v>0.50980858128075</v>
+        <v>0.421900491569101</v>
       </c>
       <c r="G72" t="n">
-        <v>0.74579590942542</v>
+        <v>0.736303474001231</v>
       </c>
       <c r="H72" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
@@ -2418,302 +2430,302 @@
         <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="F73" t="n">
-        <v>0.66107144489985</v>
+        <v>0.500126894074981</v>
       </c>
       <c r="G73" t="n">
-        <v>0.805635234120042</v>
+        <v>1.41393771862336</v>
       </c>
       <c r="H73" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="F74" t="n">
-        <v>0.493228099432038</v>
+        <v>0.367935183228812</v>
       </c>
       <c r="G74" t="n">
-        <v>0.698712456426076</v>
+        <v>0.613078683079382</v>
       </c>
       <c r="H74" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
       </c>
       <c r="D75" t="n">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="F75" t="n">
-        <v>0.646511380197521</v>
+        <v>0.491235794992377</v>
       </c>
       <c r="G75" t="n">
-        <v>0.790381932711032</v>
+        <v>1.14728897660759</v>
       </c>
       <c r="H75" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E76" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="F76" t="n">
-        <v>0.497764865490098</v>
+        <v>0.420262323849853</v>
       </c>
       <c r="G76" t="n">
-        <v>1.40428524356967</v>
+        <v>0.836749381840437</v>
       </c>
       <c r="H76" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="F77" t="n">
-        <v>0.511075405950891</v>
+        <v>0.407573711969863</v>
       </c>
       <c r="G77" t="n">
-        <v>1.17093615338684</v>
+        <v>0.812229085328596</v>
       </c>
       <c r="H77" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
       </c>
       <c r="D78" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="F78" t="n">
-        <v>0.630120744159271</v>
+        <v>0.441359638782261</v>
       </c>
       <c r="G78" t="n">
-        <v>0.819094877132137</v>
+        <v>0.711367930748626</v>
       </c>
       <c r="H78" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E79" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="F79" t="n">
-        <v>0.500126894074981</v>
+        <v>0.444207825203378</v>
       </c>
       <c r="G79" t="n">
-        <v>1.41393771862336</v>
+        <v>1.45079481811622</v>
       </c>
       <c r="H79" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="F80" t="n">
-        <v>0.564581494648128</v>
+        <v>0.503966937523387</v>
       </c>
       <c r="G80" t="n">
-        <v>0.852276440574064</v>
+        <v>0.67670304860651</v>
       </c>
       <c r="H80" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E81" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
-        <v>0.510605135030286</v>
+        <v>0.42176211212584</v>
       </c>
       <c r="G81" t="n">
-        <v>0.705195213699935</v>
+        <v>0.687315182202654</v>
       </c>
       <c r="H81" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
-        <v>0.44460148965328</v>
+        <v>0.375119888258991</v>
       </c>
       <c r="G82" t="n">
-        <v>0.709190891380632</v>
+        <v>0.638242662375072</v>
       </c>
       <c r="H82" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
         <v>10</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F83" t="n">
-        <v>0.606452454125407</v>
+        <v>0.460062929102367</v>
       </c>
       <c r="G83" t="n">
-        <v>1.25382884884297</v>
+        <v>1.32166262355803</v>
       </c>
       <c r="H83" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C84" t="s">
         <v>10</v>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E84" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F84" t="n">
-        <v>0.630586285157324</v>
+        <v>0.425649985381802</v>
       </c>
       <c r="G84" t="n">
-        <v>1.22136120098253</v>
+        <v>1.30090551024586</v>
       </c>
       <c r="H84" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="85">
@@ -2721,475 +2733,475 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C85" t="s">
         <v>10</v>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="F85" t="n">
-        <v>0.630586285157324</v>
+        <v>0.506249707447223</v>
       </c>
       <c r="G85" t="n">
-        <v>1.22136120098253</v>
+        <v>1.36864766996912</v>
       </c>
       <c r="H85" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
       </c>
       <c r="D86" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E86" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="F86" t="n">
-        <v>0.581539490513156</v>
+        <v>0.506249707447223</v>
       </c>
       <c r="G86" t="n">
-        <v>1.25782720293781</v>
+        <v>1.36864766996912</v>
       </c>
       <c r="H86" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="E87" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F87" t="n">
-        <v>0.61523915372729</v>
+        <v>0.460523353447621</v>
       </c>
       <c r="G87" t="n">
-        <v>1.33402615134227</v>
+        <v>0.852369583105289</v>
       </c>
       <c r="H87" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F88" t="n">
-        <v>0.610049737581012</v>
+        <v>0.350276777039548</v>
       </c>
       <c r="G88" t="n">
-        <v>1.16851173134946</v>
+        <v>0.640966391647602</v>
       </c>
       <c r="H88" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E89" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F89" t="n">
-        <v>0.51017516131393</v>
+        <v>0.443854836925748</v>
       </c>
       <c r="G89" t="n">
-        <v>1.19570336849286</v>
+        <v>1.29170257866098</v>
       </c>
       <c r="H89" t="n">
-        <v>0.863065497508137</v>
+        <v>0.806835471244011</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E90" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F90" t="n">
-        <v>0.607523204861397</v>
+        <v>0.515078446457236</v>
       </c>
       <c r="G90" t="n">
-        <v>1.24512044947327</v>
+        <v>1.30418993247453</v>
       </c>
       <c r="H90" t="n">
-        <v>0.863065497508137</v>
+        <v>0.808276946748278</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E91" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F91" t="n">
-        <v>0.562751791948456</v>
+        <v>0.52568181287356</v>
       </c>
       <c r="G91" t="n">
-        <v>0.824779111785415</v>
+        <v>1.41389124772656</v>
       </c>
       <c r="H91" t="n">
-        <v>0.863065497508137</v>
+        <v>0.812417347168229</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C92" t="s">
         <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E92" t="n">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="F92" t="n">
-        <v>0.458507771308714</v>
+        <v>0.200659436579709</v>
       </c>
       <c r="G92" t="n">
-        <v>0.727085218432325</v>
+        <v>0.746666649752752</v>
       </c>
       <c r="H92" t="n">
-        <v>0.863065497508137</v>
+        <v>0.818690501245212</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="E93" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F93" t="n">
-        <v>0.637077147527254</v>
+        <v>0.549951505971065</v>
       </c>
       <c r="G93" t="n">
-        <v>0.722902475292088</v>
+        <v>1.17616280777339</v>
       </c>
       <c r="H93" t="n">
-        <v>0.863065497508137</v>
+        <v>0.824927258956598</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E94" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="F94" t="n">
-        <v>0.651409377460877</v>
+        <v>0.548966792256553</v>
       </c>
       <c r="G94" t="n">
-        <v>0.753251838544302</v>
+        <v>0.805179524779994</v>
       </c>
       <c r="H94" t="n">
-        <v>0.863065497508137</v>
+        <v>0.824927258956598</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="F95" t="n">
-        <v>0.659938319970955</v>
+        <v>0.221131765677778</v>
       </c>
       <c r="G95" t="n">
-        <v>1.25721402373184</v>
+        <v>0.518988544656163</v>
       </c>
       <c r="H95" t="n">
-        <v>0.863065497508137</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E96" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="F96" t="n">
-        <v>0.574441105410319</v>
+        <v>0.280848235953145</v>
       </c>
       <c r="G96" t="n">
-        <v>0.824175642564801</v>
+        <v>1.62705717448118</v>
       </c>
       <c r="H96" t="n">
-        <v>0.863065497508137</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E97" t="n">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="F97" t="n">
-        <v>0.601725526614713</v>
+        <v>0.266215469647774</v>
       </c>
       <c r="G97" t="n">
-        <v>1.15938388712288</v>
+        <v>0.558756537763539</v>
       </c>
       <c r="H97" t="n">
-        <v>0.863065497508137</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E98" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="F98" t="n">
-        <v>0.443854836925748</v>
+        <v>0.282642017764431</v>
       </c>
       <c r="G98" t="n">
-        <v>1.29170257866098</v>
+        <v>0.661461097809395</v>
       </c>
       <c r="H98" t="n">
-        <v>0.863065497508137</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E99" t="n">
         <v>7</v>
       </c>
       <c r="F99" t="n">
-        <v>0.582413831827484</v>
+        <v>0.305049251855383</v>
       </c>
       <c r="G99" t="n">
-        <v>0.679555204847049</v>
+        <v>0.627339372083079</v>
       </c>
       <c r="H99" t="n">
-        <v>0.863065497508137</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F100" t="n">
-        <v>0.676806064659977</v>
+        <v>0.235134298411267</v>
       </c>
       <c r="G100" t="n">
-        <v>1.16333561954796</v>
+        <v>0.50321444727453</v>
       </c>
       <c r="H100" t="n">
-        <v>0.871503699699148</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="F101" t="n">
-        <v>0.689900357895171</v>
+        <v>0.237228079336741</v>
       </c>
       <c r="G101" t="n">
-        <v>0.875909517615503</v>
+        <v>1.84776965457126</v>
       </c>
       <c r="H101" t="n">
-        <v>0.876359914083055</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
         <v>26</v>
       </c>
-      <c r="B102" t="s">
-        <v>42</v>
-      </c>
       <c r="C102" t="s">
         <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="E102" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F102" t="n">
-        <v>0.266996292293019</v>
+        <v>0.298372544552273</v>
       </c>
       <c r="G102" t="n">
-        <v>1.37259052397131</v>
+        <v>0.583828821356584</v>
       </c>
       <c r="H102" t="n">
-        <v>0.879878231134594</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
@@ -3207,67 +3219,67 @@
         <v>0.664250877427568</v>
       </c>
       <c r="H103" t="n">
-        <v>0.879878231134594</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E104" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F104" t="n">
-        <v>0.718063164569744</v>
+        <v>0.290101817980223</v>
       </c>
       <c r="G104" t="n">
-        <v>1.20643732771962</v>
+        <v>1.41309492030293</v>
       </c>
       <c r="H104" t="n">
-        <v>0.890308023368971</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B105" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E105" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F105" t="n">
-        <v>0.719823508255764</v>
+        <v>0.278055824180454</v>
       </c>
       <c r="G105" t="n">
-        <v>0.837021648649028</v>
+        <v>1.67174349422142</v>
       </c>
       <c r="H105" t="n">
-        <v>0.890308023368971</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
@@ -3276,328 +3288,328 @@
         <v>16</v>
       </c>
       <c r="E106" t="n">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="F106" t="n">
-        <v>0.734400488000406</v>
+        <v>0.256294234330313</v>
       </c>
       <c r="G106" t="n">
-        <v>0.878694305655846</v>
+        <v>1.58538658668626</v>
       </c>
       <c r="H106" t="n">
-        <v>0.896540855481015</v>
+        <v>0.840946586195921</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B107" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C107" t="s">
         <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E107" t="n">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="F107" t="n">
-        <v>0.301493880642793</v>
+        <v>0.570218121223652</v>
       </c>
       <c r="G107" t="n">
-        <v>1.45774089403741</v>
+        <v>1.32613229544727</v>
       </c>
       <c r="H107" t="n">
-        <v>0.900736628993074</v>
+        <v>0.842931135721921</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B108" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" t="n">
+        <v>62</v>
+      </c>
+      <c r="E108" t="n">
         <v>41</v>
       </c>
-      <c r="C108" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3</v>
-      </c>
-      <c r="E108" t="n">
-        <v>29</v>
-      </c>
       <c r="F108" t="n">
-        <v>0.303509081508536</v>
+        <v>0.330798984350319</v>
       </c>
       <c r="G108" t="n">
-        <v>0.453266823745936</v>
+        <v>1.32136851193317</v>
       </c>
       <c r="H108" t="n">
-        <v>0.900736628993074</v>
+        <v>0.846514292557638</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C109" t="s">
         <v>10</v>
       </c>
       <c r="D109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E109" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F109" t="n">
-        <v>0.298372544552273</v>
+        <v>0.335277463617096</v>
       </c>
       <c r="G109" t="n">
-        <v>0.583828821356584</v>
+        <v>0.515825014526562</v>
       </c>
       <c r="H109" t="n">
-        <v>0.900736628993074</v>
+        <v>0.846514292557638</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C110" t="s">
         <v>10</v>
       </c>
       <c r="D110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="F110" t="n">
-        <v>0.767149258515491</v>
+        <v>0.328742310242566</v>
       </c>
       <c r="G110" t="n">
-        <v>1.10233457996624</v>
+        <v>0.577378436852331</v>
       </c>
       <c r="H110" t="n">
-        <v>0.912810510132356</v>
+        <v>0.846514292557638</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
       </c>
       <c r="D111" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="E111" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="F111" t="n">
-        <v>0.766992581343509</v>
+        <v>0.340265548969247</v>
       </c>
       <c r="G111" t="n">
-        <v>1.06782716294781</v>
+        <v>0.714914031919502</v>
       </c>
       <c r="H111" t="n">
-        <v>0.912810510132356</v>
+        <v>0.846514292557638</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
         <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E112" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="F112" t="n">
-        <v>0.367935183228812</v>
+        <v>0.507460860318893</v>
       </c>
       <c r="G112" t="n">
-        <v>0.613078683079382</v>
+        <v>1.47685567949947</v>
       </c>
       <c r="H112" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
         <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E113" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F113" t="n">
-        <v>0.371491397342271</v>
+        <v>0.409809468609867</v>
       </c>
       <c r="G113" t="n">
-        <v>0.60295244347598</v>
+        <v>0.794281386808552</v>
       </c>
       <c r="H113" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C114" t="s">
         <v>10</v>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="F114" t="n">
-        <v>0.328742310242566</v>
+        <v>0.497764865490098</v>
       </c>
       <c r="G114" t="n">
-        <v>0.577378436852331</v>
+        <v>1.40428524356967</v>
       </c>
       <c r="H114" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B115" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
       </c>
       <c r="D115" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E115" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="F115" t="n">
-        <v>0.360036922887737</v>
+        <v>0.421900491569101</v>
       </c>
       <c r="G115" t="n">
-        <v>0.719058302138559</v>
+        <v>0.736303474001231</v>
       </c>
       <c r="H115" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C116" t="s">
         <v>10</v>
       </c>
       <c r="D116" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E116" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F116" t="n">
-        <v>0.349942905872178</v>
+        <v>0.483069501530197</v>
       </c>
       <c r="G116" t="n">
-        <v>0.671962952762743</v>
+        <v>1.29313861107325</v>
       </c>
       <c r="H116" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B117" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
         <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E117" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="F117" t="n">
-        <v>0.33959255376214</v>
+        <v>0.367935183228812</v>
       </c>
       <c r="G117" t="n">
-        <v>1.47007645723898</v>
+        <v>0.613078683079382</v>
       </c>
       <c r="H117" t="n">
-        <v>0.923708339337539</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B118" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C118" t="s">
         <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E118" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="F118" t="n">
-        <v>0.826247464663013</v>
+        <v>0.456734464480454</v>
       </c>
       <c r="G118" t="n">
-        <v>0.949378550539976</v>
+        <v>0.770908037278027</v>
       </c>
       <c r="H118" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="119">
@@ -3605,25 +3617,25 @@
         <v>30</v>
       </c>
       <c r="B119" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C119" t="s">
         <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="E119" t="n">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="F119" t="n">
-        <v>0.877075564945529</v>
+        <v>0.495506681056477</v>
       </c>
       <c r="G119" t="n">
-        <v>1.08296369820383</v>
+        <v>1.16018685349986</v>
       </c>
       <c r="H119" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="120">
@@ -3631,181 +3643,181 @@
         <v>30</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C120" t="s">
         <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E120" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="F120" t="n">
-        <v>0.838406206681569</v>
+        <v>0.506718666169583</v>
       </c>
       <c r="G120" t="n">
-        <v>0.855193485414019</v>
+        <v>0.807867625590243</v>
       </c>
       <c r="H120" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B121" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C121" t="s">
         <v>10</v>
       </c>
       <c r="D121" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E121" t="n">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="F121" t="n">
-        <v>0.874156219281355</v>
+        <v>0.441359638782261</v>
       </c>
       <c r="G121" t="n">
-        <v>1.09484982566731</v>
+        <v>0.711367930748626</v>
       </c>
       <c r="H121" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B122" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
         <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="E122" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F122" t="n">
-        <v>0.871532422183086</v>
+        <v>0.483292446606362</v>
       </c>
       <c r="G122" t="n">
-        <v>1.1070461941951</v>
+        <v>1.20157656622878</v>
       </c>
       <c r="H122" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E123" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F123" t="n">
-        <v>0.846438692991156</v>
+        <v>0.444207825203378</v>
       </c>
       <c r="G123" t="n">
-        <v>1.14781148799108</v>
+        <v>1.45079481811622</v>
       </c>
       <c r="H123" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B124" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C124" t="s">
         <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E124" t="n">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="F124" t="n">
-        <v>0.850987713461625</v>
+        <v>0.375119888258991</v>
       </c>
       <c r="G124" t="n">
-        <v>0.874336639106086</v>
+        <v>0.638242662375072</v>
       </c>
       <c r="H124" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s">
         <v>47</v>
       </c>
-      <c r="B125" t="s">
-        <v>49</v>
-      </c>
       <c r="C125" t="s">
         <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E125" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="F125" t="n">
-        <v>0.863757958374014</v>
+        <v>0.460062929102367</v>
       </c>
       <c r="G125" t="n">
-        <v>1.11283987073959</v>
+        <v>1.32166262355803</v>
       </c>
       <c r="H125" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C126" t="s">
         <v>10</v>
       </c>
       <c r="D126" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E126" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F126" t="n">
-        <v>0.836270940264214</v>
+        <v>0.494943210054961</v>
       </c>
       <c r="G126" t="n">
-        <v>1.05922374950497</v>
+        <v>1.42903658711332</v>
       </c>
       <c r="H126" t="n">
-        <v>0.936876171646361</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="127">
@@ -3813,285 +3825,285 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C127" t="s">
         <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E127" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="F127" t="n">
-        <v>0.39022905751721</v>
+        <v>0.35832302315129</v>
       </c>
       <c r="G127" t="n">
-        <v>1.50080804067479</v>
+        <v>1.60438484332656</v>
       </c>
       <c r="H127" t="n">
-        <v>0.944765086620613</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C128" t="s">
         <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E128" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="F128" t="n">
-        <v>0.409809468609867</v>
+        <v>0.506249707447223</v>
       </c>
       <c r="G128" t="n">
-        <v>0.794281386808552</v>
+        <v>1.36864766996912</v>
       </c>
       <c r="H128" t="n">
-        <v>0.966730028515585</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C129" t="s">
         <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E129" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="F129" t="n">
-        <v>0.44460148965328</v>
+        <v>0.456847846195203</v>
       </c>
       <c r="G129" t="n">
-        <v>0.709190891380632</v>
+        <v>0.843204264970705</v>
       </c>
       <c r="H129" t="n">
-        <v>0.967738358683678</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C130" t="s">
         <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="E130" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F130" t="n">
-        <v>0.452312493732589</v>
+        <v>0.350276777039548</v>
       </c>
       <c r="G130" t="n">
-        <v>1.23182490445609</v>
+        <v>0.640966391647602</v>
       </c>
       <c r="H130" t="n">
-        <v>0.967738358683678</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B131" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
         <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E131" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F131" t="n">
-        <v>0.433141456599037</v>
+        <v>0.443854836925748</v>
       </c>
       <c r="G131" t="n">
-        <v>1.30174121161204</v>
+        <v>1.29170257866098</v>
       </c>
       <c r="H131" t="n">
-        <v>0.967738358683678</v>
+        <v>0.848541110697165</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C132" t="s">
         <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E132" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F132" t="n">
-        <v>0.443854836925748</v>
+        <v>0.522206944328555</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29170257866098</v>
+        <v>1.23487923137555</v>
       </c>
       <c r="H132" t="n">
-        <v>0.967738358683678</v>
+        <v>0.859114650346977</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
         <v>10</v>
       </c>
       <c r="D133" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E133" t="n">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>0.920664915667375</v>
+        <v>0.530985751733577</v>
       </c>
       <c r="G133" t="n">
-        <v>1.03404783407983</v>
+        <v>1.19808020205604</v>
       </c>
       <c r="H133" t="n">
-        <v>0.972387663738576</v>
+        <v>0.859691217092458</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C134" t="s">
         <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E134" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="F134" t="n">
-        <v>0.466503790795471</v>
+        <v>0.548966792256553</v>
       </c>
       <c r="G134" t="n">
-        <v>0.784298828962988</v>
+        <v>0.805179524779994</v>
       </c>
       <c r="H134" t="n">
-        <v>0.975417017117803</v>
+        <v>0.874915825158881</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C135" t="s">
         <v>10</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E135" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F135" t="n">
-        <v>0.502959339417172</v>
+        <v>0.557831420967053</v>
       </c>
       <c r="G135" t="n">
-        <v>0.692725032814135</v>
+        <v>0.81298190766099</v>
       </c>
       <c r="H135" t="n">
-        <v>0.995316810447997</v>
+        <v>0.875366229825222</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>23</v>
+      </c>
+      <c r="B136" t="s">
         <v>48</v>
       </c>
-      <c r="B136" t="s">
-        <v>43</v>
-      </c>
       <c r="C136" t="s">
         <v>10</v>
       </c>
       <c r="D136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E136" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="F136" t="n">
-        <v>0.646511380197521</v>
+        <v>0.570218121223652</v>
       </c>
       <c r="G136" t="n">
-        <v>0.790381932711032</v>
+        <v>1.32613229544727</v>
       </c>
       <c r="H136" t="n">
-        <v>0.995316810447997</v>
+        <v>0.881246187345645</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
         <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E137" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="F137" t="n">
-        <v>0.497764865490098</v>
+        <v>0.656031778652162</v>
       </c>
       <c r="G137" t="n">
-        <v>1.40428524356967</v>
+        <v>0.788592561767121</v>
       </c>
       <c r="H137" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="138">
@@ -4099,446 +4111,446 @@
         <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C138" t="s">
         <v>10</v>
       </c>
       <c r="D138" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E138" t="n">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="F138" t="n">
-        <v>0.630120744159271</v>
+        <v>0.676806064659977</v>
       </c>
       <c r="G138" t="n">
-        <v>0.819094877132137</v>
+        <v>1.16333561954796</v>
       </c>
       <c r="H138" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C139" t="s">
         <v>10</v>
       </c>
       <c r="D139" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="E139" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="F139" t="n">
-        <v>0.564581494648128</v>
+        <v>0.682766935282337</v>
       </c>
       <c r="G139" t="n">
-        <v>0.852276440574064</v>
+        <v>0.829147013792629</v>
       </c>
       <c r="H139" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
         <v>10</v>
       </c>
       <c r="D140" t="n">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="E140" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="F140" t="n">
-        <v>0.626056371536728</v>
+        <v>0.621987350771959</v>
       </c>
       <c r="G140" t="n">
-        <v>1.10280725617814</v>
+        <v>1.27280000664737</v>
       </c>
       <c r="H140" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C141" t="s">
         <v>10</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E141" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="F141" t="n">
-        <v>0.606452454125407</v>
+        <v>0.61523915372729</v>
       </c>
       <c r="G141" t="n">
-        <v>1.25382884884297</v>
+        <v>1.33402615134227</v>
       </c>
       <c r="H141" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
       </c>
       <c r="D142" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E142" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
-        <v>0.657994050273593</v>
+        <v>0.703405750354896</v>
       </c>
       <c r="G142" t="n">
-        <v>1.26975463370625</v>
+        <v>1.10385314529785</v>
       </c>
       <c r="H142" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C143" t="s">
         <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E143" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F143" t="n">
-        <v>0.581539490513156</v>
+        <v>0.695484616740845</v>
       </c>
       <c r="G143" t="n">
-        <v>1.25782720293781</v>
+        <v>1.1380145178319</v>
       </c>
       <c r="H143" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C144" t="s">
         <v>10</v>
       </c>
       <c r="D144" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E144" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F144" t="n">
-        <v>0.61523915372729</v>
+        <v>0.662281264954675</v>
       </c>
       <c r="G144" t="n">
-        <v>1.33402615134227</v>
+        <v>0.854942528910744</v>
       </c>
       <c r="H144" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B145" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C145" t="s">
         <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E145" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F145" t="n">
-        <v>0.59388057923439</v>
+        <v>0.637077147527254</v>
       </c>
       <c r="G145" t="n">
-        <v>1.18838132870469</v>
+        <v>0.722902475292088</v>
       </c>
       <c r="H145" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B146" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C146" t="s">
         <v>10</v>
       </c>
       <c r="D146" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E146" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F146" t="n">
-        <v>0.607523204861397</v>
+        <v>0.651409377460877</v>
       </c>
       <c r="G146" t="n">
-        <v>1.24512044947327</v>
+        <v>0.753251838544302</v>
       </c>
       <c r="H146" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C147" t="s">
         <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E147" t="n">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>0.60960398069094</v>
+        <v>0.663012058402754</v>
       </c>
       <c r="G147" t="n">
-        <v>0.695857133745228</v>
+        <v>1.16494331419245</v>
       </c>
       <c r="H147" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C148" t="s">
         <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E148" t="n">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="F148" t="n">
-        <v>0.659938319970955</v>
+        <v>0.699179681198832</v>
       </c>
       <c r="G148" t="n">
-        <v>1.25721402373184</v>
+        <v>1.12799460199462</v>
       </c>
       <c r="H148" t="n">
-        <v>0.995316810447997</v>
+        <v>0.88577020415061</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B149" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E149" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="F149" t="n">
-        <v>0.607958595346604</v>
+        <v>0.719823508255764</v>
       </c>
       <c r="G149" t="n">
-        <v>1.16793407587681</v>
+        <v>0.837021648649028</v>
       </c>
       <c r="H149" t="n">
-        <v>0.995316810447997</v>
+        <v>0.895390217586438</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B150" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C150" t="s">
         <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E150" t="n">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F150" t="n">
-        <v>0.525314006026836</v>
+        <v>0.589042267367359</v>
       </c>
       <c r="G150" t="n">
-        <v>0.794340978801389</v>
+        <v>1.24802574892841</v>
       </c>
       <c r="H150" t="n">
-        <v>0.995316810447997</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E151" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="F151" t="n">
-        <v>0.601725526614713</v>
+        <v>0.61523915372729</v>
       </c>
       <c r="G151" t="n">
-        <v>1.15938388712288</v>
+        <v>1.33402615134227</v>
       </c>
       <c r="H151" t="n">
-        <v>0.995316810447997</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
+        <v>54</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" t="n">
         <v>25</v>
       </c>
-      <c r="B152" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" t="s">
-        <v>10</v>
-      </c>
-      <c r="D152" t="n">
-        <v>27</v>
-      </c>
-      <c r="E152" t="n">
-        <v>13</v>
-      </c>
       <c r="F152" t="n">
-        <v>0.824100937452876</v>
+        <v>0.60960398069094</v>
       </c>
       <c r="G152" t="n">
-        <v>1.13727602674493</v>
+        <v>0.695857133745228</v>
       </c>
       <c r="H152" t="n">
-        <v>0.997799635393051</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C153" t="s">
         <v>10</v>
       </c>
       <c r="D153" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E153" t="n">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F153" t="n">
-        <v>0.824856009792112</v>
+        <v>0.615173320702119</v>
       </c>
       <c r="G153" t="n">
-        <v>0.851361680460712</v>
+        <v>1.13741434866417</v>
       </c>
       <c r="H153" t="n">
-        <v>0.997799635393051</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C154" t="s">
         <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E154" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F154" t="n">
-        <v>0.889343153285111</v>
+        <v>0.739905876333053</v>
       </c>
       <c r="G154" t="n">
-        <v>1.07659802592796</v>
+        <v>1.11884130194171</v>
       </c>
       <c r="H154" t="n">
-        <v>0.997799635393051</v>
+        <v>0.8985985618128</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B155" t="s">
         <v>56</v>
@@ -4547,287 +4559,287 @@
         <v>10</v>
       </c>
       <c r="D155" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E155" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="F155" t="n">
-        <v>0.826247464663013</v>
+        <v>0.740022345022306</v>
       </c>
       <c r="G155" t="n">
-        <v>0.949378550539976</v>
+        <v>0.852211314182209</v>
       </c>
       <c r="H155" t="n">
-        <v>0.997799635393051</v>
+        <v>0.8985985618128</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E156" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="F156" t="n">
-        <v>0.888748282514609</v>
+        <v>0.752386008643869</v>
       </c>
       <c r="G156" t="n">
-        <v>0.933230017639413</v>
+        <v>1.13924181298246</v>
       </c>
       <c r="H156" t="n">
-        <v>0.997799635393051</v>
+        <v>0.902863210372642</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
         <v>10</v>
       </c>
       <c r="D157" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E157" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="F157" t="n">
-        <v>0.877075564945529</v>
+        <v>0.787956947251514</v>
       </c>
       <c r="G157" t="n">
-        <v>1.08296369820383</v>
+        <v>0.920344778245268</v>
       </c>
       <c r="H157" t="n">
-        <v>0.997799635393051</v>
+        <v>0.934553588600633</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B158" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C158" t="s">
         <v>10</v>
       </c>
       <c r="D158" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E158" t="n">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="F158" t="n">
-        <v>0.838406206681569</v>
+        <v>0.79993387992526</v>
       </c>
       <c r="G158" t="n">
-        <v>0.855193485414019</v>
+        <v>0.895731232480841</v>
       </c>
       <c r="H158" t="n">
-        <v>0.997799635393051</v>
+        <v>0.937853514395132</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C159" t="s">
         <v>10</v>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E159" t="n">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="F159" t="n">
-        <v>0.794654902688309</v>
+        <v>0.675492431235448</v>
       </c>
       <c r="G159" t="n">
-        <v>1.19707829350396</v>
+        <v>0.876598903213946</v>
       </c>
       <c r="H159" t="n">
-        <v>0.997799635393051</v>
+        <v>0.943838739534462</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B160" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C160" t="s">
         <v>10</v>
       </c>
       <c r="D160" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E160" t="n">
         <v>76</v>
       </c>
       <c r="F160" t="n">
-        <v>0.889064513817736</v>
+        <v>0.671822613423403</v>
       </c>
       <c r="G160" t="n">
-        <v>0.950568869891571</v>
+        <v>0.788011043142846</v>
       </c>
       <c r="H160" t="n">
-        <v>0.997799635393051</v>
+        <v>0.943838739534462</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C161" t="s">
         <v>10</v>
       </c>
       <c r="D161" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E161" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="F161" t="n">
-        <v>0.874156219281355</v>
+        <v>0.663012058402754</v>
       </c>
       <c r="G161" t="n">
-        <v>1.09484982566731</v>
+        <v>1.16494331419245</v>
       </c>
       <c r="H161" t="n">
-        <v>0.997799635393051</v>
+        <v>0.943838739534462</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C162" t="s">
         <v>10</v>
       </c>
       <c r="D162" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E162" t="n">
         <v>73</v>
       </c>
       <c r="F162" t="n">
-        <v>0.840496126542468</v>
+        <v>0.693485512559769</v>
       </c>
       <c r="G162" t="n">
-        <v>1.09221261424539</v>
+        <v>1.1227782485891</v>
       </c>
       <c r="H162" t="n">
-        <v>0.997799635393051</v>
+        <v>0.950884366430412</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C163" t="s">
         <v>10</v>
       </c>
       <c r="D163" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E163" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F163" t="n">
-        <v>0.724901985430724</v>
+        <v>0.699179681198832</v>
       </c>
       <c r="G163" t="n">
-        <v>1.1658383841768</v>
+        <v>1.12799460199462</v>
       </c>
       <c r="H163" t="n">
-        <v>0.997799635393051</v>
+        <v>0.950884366430412</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C164" t="s">
         <v>10</v>
       </c>
       <c r="D164" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E164" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="F164" t="n">
-        <v>0.877313522179666</v>
+        <v>0.739905876333053</v>
       </c>
       <c r="G164" t="n">
-        <v>0.927902365666384</v>
+        <v>1.11884130194171</v>
       </c>
       <c r="H164" t="n">
-        <v>0.997799635393051</v>
+        <v>0.955471888509812</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B165" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C165" t="s">
         <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E165" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F165" t="n">
-        <v>0.846438692991156</v>
+        <v>0.719823508255764</v>
       </c>
       <c r="G165" t="n">
-        <v>1.14781148799108</v>
+        <v>0.837021648649028</v>
       </c>
       <c r="H165" t="n">
-        <v>0.997799635393051</v>
+        <v>0.955471888509812</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C166" t="s">
         <v>10</v>
@@ -4836,561 +4848,1029 @@
         <v>17</v>
       </c>
       <c r="E166" t="n">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="F166" t="n">
-        <v>0.719823508255764</v>
+        <v>0.740022345022306</v>
       </c>
       <c r="G166" t="n">
-        <v>0.837021648649028</v>
+        <v>0.852211314182209</v>
       </c>
       <c r="H166" t="n">
-        <v>0.997799635393051</v>
+        <v>0.955471888509812</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C167" t="s">
         <v>10</v>
       </c>
       <c r="D167" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E167" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F167" t="n">
-        <v>0.850987713461625</v>
+        <v>0.734328018829328</v>
       </c>
       <c r="G167" t="n">
-        <v>0.874336639106086</v>
+        <v>1.18224953296244</v>
       </c>
       <c r="H167" t="n">
-        <v>0.997799635393051</v>
+        <v>0.955471888509812</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B168" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C168" t="s">
         <v>10</v>
       </c>
       <c r="D168" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="E168" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="F168" t="n">
-        <v>0.863433754187614</v>
+        <v>0.828162836498807</v>
       </c>
       <c r="G168" t="n">
-        <v>0.925332601310225</v>
+        <v>1.06842307575696</v>
       </c>
       <c r="H168" t="n">
-        <v>0.997799635393051</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C169" t="s">
         <v>10</v>
       </c>
       <c r="D169" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="E169" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F169" t="n">
-        <v>0.750051425678478</v>
+        <v>0.798572311377042</v>
       </c>
       <c r="G169" t="n">
-        <v>0.922586089251779</v>
+        <v>1.14444019035117</v>
       </c>
       <c r="H169" t="n">
-        <v>0.997799635393051</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C170" t="s">
         <v>10</v>
       </c>
       <c r="D170" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E170" t="n">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="F170" t="n">
-        <v>0.863757958374014</v>
+        <v>0.76621605385296</v>
       </c>
       <c r="G170" t="n">
-        <v>1.11283987073959</v>
+        <v>1.13417848103365</v>
       </c>
       <c r="H170" t="n">
-        <v>0.997799635393051</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B171" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
         <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E171" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.836525507138017</v>
+        <v>0.822025072862908</v>
       </c>
       <c r="G171" t="n">
-        <v>1.05022093464666</v>
+        <v>1.19787692165925</v>
       </c>
       <c r="H171" t="n">
-        <v>0.997799635393051</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
         <v>10</v>
       </c>
       <c r="D172" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E172" t="n">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="F172" t="n">
-        <v>0.842013883992078</v>
+        <v>0.795949228127607</v>
       </c>
       <c r="G172" t="n">
-        <v>1.13924465480846</v>
+        <v>1.10926392255017</v>
       </c>
       <c r="H172" t="n">
-        <v>0.997799635393051</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
         <v>33</v>
       </c>
-      <c r="B173" t="s">
-        <v>24</v>
-      </c>
       <c r="C173" t="s">
         <v>10</v>
       </c>
       <c r="D173" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="E173" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0.838312707433428</v>
       </c>
       <c r="G173" t="n">
-        <v>1.03387619150675</v>
+        <v>0.854886587861007</v>
       </c>
       <c r="H173" t="n">
-        <v>1</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B174" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C174" t="s">
         <v>10</v>
       </c>
       <c r="D174" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E174" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>0.821203373879971</v>
       </c>
       <c r="G174" t="n">
-        <v>1.04973944351004</v>
+        <v>0.861460187672589</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C175" t="s">
         <v>10</v>
       </c>
       <c r="D175" t="n">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="E175" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>0.834570051106879</v>
       </c>
       <c r="G175" t="n">
-        <v>1.00697476830707</v>
+        <v>0.828679750031405</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B176" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C176" t="s">
         <v>10</v>
       </c>
       <c r="D176" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E176" t="n">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0.805012807215326</v>
       </c>
       <c r="G176" t="n">
-        <v>0.976681438537669</v>
+        <v>1.28261943784646</v>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>0.971680638161474</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
       </c>
       <c r="D177" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E177" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0.889343153285111</v>
       </c>
       <c r="G177" t="n">
-        <v>1.01954131783174</v>
+        <v>1.07659802592796</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0.975408619732057</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B178" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C178" t="s">
         <v>10</v>
       </c>
       <c r="D178" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E178" t="n">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0.888249516478311</v>
       </c>
       <c r="G178" t="n">
-        <v>0.998950108344961</v>
+        <v>1.06462147589472</v>
       </c>
       <c r="H178" t="n">
-        <v>1</v>
+        <v>0.975408619732057</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C179" t="s">
         <v>10</v>
       </c>
       <c r="D179" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="E179" t="n">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="F179" t="n">
-        <v>0.913519245929117</v>
+        <v>0.879183822333398</v>
       </c>
       <c r="G179" t="n">
-        <v>1.03535355231298</v>
+        <v>0.910732899711824</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>0.975408619732057</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C180" t="s">
         <v>10</v>
       </c>
       <c r="D180" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E180" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="F180" t="n">
-        <v>0.920664915667375</v>
+        <v>0.874156219281355</v>
       </c>
       <c r="G180" t="n">
-        <v>1.03404783407983</v>
+        <v>1.09484982566731</v>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>0.975408619732057</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B181" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="E181" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.878169474350505</v>
       </c>
       <c r="G181" t="n">
-        <v>1.06731017927794</v>
+        <v>1.06703209690045</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>0.975408619732057</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B182" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C182" t="s">
         <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E182" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>0.912003993992927</v>
       </c>
       <c r="G182" t="n">
-        <v>1.03669384395501</v>
+        <v>0.964353269129536</v>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>0.979204288287143</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B183" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C183" t="s">
         <v>10</v>
       </c>
       <c r="D183" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E183" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>0.908290113368219</v>
       </c>
       <c r="G183" t="n">
-        <v>1.05202469792314</v>
+        <v>0.94803852830346</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>0.979204288287143</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B184" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C184" t="s">
         <v>10</v>
       </c>
       <c r="D184" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="E184" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>0.912403642779507</v>
       </c>
       <c r="G184" t="n">
-        <v>0.918718624991361</v>
+        <v>1.04721205774363</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>0.990055016633082</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B185" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C185" t="s">
         <v>10</v>
       </c>
       <c r="D185" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E185" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>0.912003993992927</v>
       </c>
       <c r="G185" t="n">
-        <v>0.92524025879153</v>
+        <v>0.964353269129536</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>0.990055016633082</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B186" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C186" t="s">
         <v>10</v>
       </c>
       <c r="D186" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="E186" t="n">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>0.908290113368219</v>
       </c>
       <c r="G186" t="n">
-        <v>0.976681438537669</v>
+        <v>0.94803852830346</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>0.990055016633082</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B187" t="s">
+        <v>66</v>
+      </c>
+      <c r="C187" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" t="n">
+        <v>26</v>
+      </c>
+      <c r="E187" t="n">
+        <v>158</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.888249516478311</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1.06462147589472</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.990055016633082</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>30</v>
+      </c>
+      <c r="B188" t="s">
+        <v>52</v>
+      </c>
+      <c r="C188" t="s">
+        <v>10</v>
+      </c>
+      <c r="D188" t="n">
+        <v>20</v>
+      </c>
+      <c r="E188" t="n">
+        <v>164</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.879183822333398</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.910732899711824</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.990055016633082</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>12</v>
+      </c>
+      <c r="B189" t="s">
         <v>43</v>
       </c>
-      <c r="C187" t="s">
-        <v>10</v>
-      </c>
-      <c r="D187" t="n">
+      <c r="C189" t="s">
+        <v>10</v>
+      </c>
+      <c r="D189" t="n">
+        <v>23</v>
+      </c>
+      <c r="E189" t="n">
+        <v>91</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.874156219281355</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.09484982566731</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.990055016633082</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>25</v>
+      </c>
+      <c r="B190" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" t="n">
+        <v>16</v>
+      </c>
+      <c r="E190" t="n">
+        <v>69</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.861778596646391</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.88510580311927</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.990055016633082</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>55</v>
+      </c>
+      <c r="B191" t="s">
+        <v>45</v>
+      </c>
+      <c r="C191" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191" t="n">
         <v>17</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E191" t="n">
+        <v>11</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.0531969164968</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>38</v>
+      </c>
+      <c r="B192" t="s">
+        <v>24</v>
+      </c>
+      <c r="C192" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192" t="n">
+        <v>24</v>
+      </c>
+      <c r="E192" t="n">
+        <v>130</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.00920535270276</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>30</v>
+      </c>
+      <c r="B193" t="s">
+        <v>58</v>
+      </c>
+      <c r="C193" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" t="n">
+        <v>83</v>
+      </c>
+      <c r="E193" t="n">
+        <v>101</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.993299269599277</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>24</v>
+      </c>
+      <c r="C194" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194" t="n">
         <v>7</v>
       </c>
-      <c r="F187" t="n">
+      <c r="E194" t="n">
+        <v>25</v>
+      </c>
+      <c r="F194" t="n">
         <v>1</v>
       </c>
-      <c r="G187" t="n">
-        <v>1.14401577168192</v>
-      </c>
-      <c r="H187" t="n">
+      <c r="G194" t="n">
+        <v>1.00795842400206</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>43</v>
+      </c>
+      <c r="C195" t="s">
+        <v>10</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>28</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.00710578697379</v>
+      </c>
+      <c r="H195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>40</v>
+      </c>
+      <c r="B196" t="s">
+        <v>21</v>
+      </c>
+      <c r="C196" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" t="n">
+        <v>76</v>
+      </c>
+      <c r="E196" t="n">
+        <v>8</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.10573525310742</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" t="s">
+        <v>41</v>
+      </c>
+      <c r="C197" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197" t="n">
+        <v>17</v>
+      </c>
+      <c r="E197" t="n">
+        <v>153</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.939530147613745</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>53</v>
+      </c>
+      <c r="B198" t="s">
+        <v>39</v>
+      </c>
+      <c r="C198" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198" t="n">
+        <v>5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>19</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.878282455885061</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>55</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="s">
+        <v>10</v>
+      </c>
+      <c r="D199" t="n">
+        <v>14</v>
+      </c>
+      <c r="E199" t="n">
+        <v>14</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.947840660659882</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>55</v>
+      </c>
+      <c r="B200" t="s">
+        <v>46</v>
+      </c>
+      <c r="C200" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" t="n">
+        <v>17</v>
+      </c>
+      <c r="E200" t="n">
+        <v>11</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.0531969164968</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>38</v>
+      </c>
+      <c r="B201" t="s">
+        <v>26</v>
+      </c>
+      <c r="C201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201" t="n">
+        <v>23</v>
+      </c>
+      <c r="E201" t="n">
+        <v>131</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.959900155721854</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>30</v>
+      </c>
+      <c r="B202" t="s">
+        <v>62</v>
+      </c>
+      <c r="C202" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202" t="n">
+        <v>83</v>
+      </c>
+      <c r="E202" t="n">
+        <v>101</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.993299269599277</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>15</v>
+      </c>
+      <c r="B203" t="s">
+        <v>48</v>
+      </c>
+      <c r="C203" t="s">
+        <v>10</v>
+      </c>
+      <c r="D203" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" t="n">
+        <v>28</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1.00710578697379</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>17</v>
+      </c>
+      <c r="B204" t="s">
+        <v>67</v>
+      </c>
+      <c r="C204" t="s">
+        <v>10</v>
+      </c>
+      <c r="D204" t="n">
+        <v>6</v>
+      </c>
+      <c r="E204" t="n">
+        <v>92</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1.05202469792314</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" t="s">
+        <v>49</v>
+      </c>
+      <c r="C205" t="s">
+        <v>10</v>
+      </c>
+      <c r="D205" t="n">
+        <v>17</v>
+      </c>
+      <c r="E205" t="n">
+        <v>153</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.939530147613745</v>
+      </c>
+      <c r="H205" t="n">
         <v>1</v>
       </c>
     </row>

--- a/sup_tables/sup_table_s15_sex_bias.xlsx
+++ b/sup_tables/sup_table_s15_sex_bias.xlsx
@@ -4103,223 +4103,223 @@
         <v>0.788592561767121</v>
       </c>
       <c r="H137" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
         <v>10</v>
       </c>
       <c r="D138" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="E138" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F138" t="n">
-        <v>0.676806064659977</v>
+        <v>0.621987350771959</v>
       </c>
       <c r="G138" t="n">
-        <v>1.16333561954796</v>
+        <v>1.27280000664737</v>
       </c>
       <c r="H138" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C139" t="s">
         <v>10</v>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E139" t="n">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="F139" t="n">
-        <v>0.682766935282337</v>
+        <v>0.61523915372729</v>
       </c>
       <c r="G139" t="n">
-        <v>0.829147013792629</v>
+        <v>1.33402615134227</v>
       </c>
       <c r="H139" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C140" t="s">
         <v>10</v>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E140" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="F140" t="n">
-        <v>0.621987350771959</v>
+        <v>0.662281264954675</v>
       </c>
       <c r="G140" t="n">
-        <v>1.27280000664737</v>
+        <v>0.854942528910744</v>
       </c>
       <c r="H140" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="B141" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C141" t="s">
         <v>10</v>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E141" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="F141" t="n">
-        <v>0.61523915372729</v>
+        <v>0.637077147527254</v>
       </c>
       <c r="G141" t="n">
-        <v>1.33402615134227</v>
+        <v>0.722902475292088</v>
       </c>
       <c r="H141" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B142" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
       </c>
       <c r="D142" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E142" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="F142" t="n">
-        <v>0.703405750354896</v>
+        <v>0.651409377460877</v>
       </c>
       <c r="G142" t="n">
-        <v>1.10385314529785</v>
+        <v>0.753251838544302</v>
       </c>
       <c r="H142" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C143" t="s">
         <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E143" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="F143" t="n">
-        <v>0.695484616740845</v>
+        <v>0.663012058402754</v>
       </c>
       <c r="G143" t="n">
-        <v>1.1380145178319</v>
+        <v>1.16494331419245</v>
       </c>
       <c r="H143" t="n">
-        <v>0.88577020415061</v>
+        <v>0.889831973119485</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B144" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C144" t="s">
         <v>10</v>
       </c>
       <c r="D144" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E144" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="F144" t="n">
-        <v>0.662281264954675</v>
+        <v>0.589042267367359</v>
       </c>
       <c r="G144" t="n">
-        <v>0.854942528910744</v>
+        <v>1.24802574892841</v>
       </c>
       <c r="H144" t="n">
-        <v>0.88577020415061</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C145" t="s">
         <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E145" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="F145" t="n">
-        <v>0.637077147527254</v>
+        <v>0.61523915372729</v>
       </c>
       <c r="G145" t="n">
-        <v>0.722902475292088</v>
+        <v>1.33402615134227</v>
       </c>
       <c r="H145" t="n">
-        <v>0.88577020415061</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B146" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C146" t="s">
         <v>10</v>
@@ -4328,16 +4328,16 @@
         <v>9</v>
       </c>
       <c r="E146" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="F146" t="n">
-        <v>0.651409377460877</v>
+        <v>0.60960398069094</v>
       </c>
       <c r="G146" t="n">
-        <v>0.753251838544302</v>
+        <v>0.695857133745228</v>
       </c>
       <c r="H146" t="n">
-        <v>0.88577020415061</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="147">
@@ -4345,207 +4345,207 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C147" t="s">
         <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E147" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F147" t="n">
-        <v>0.663012058402754</v>
+        <v>0.615173320702119</v>
       </c>
       <c r="G147" t="n">
-        <v>1.16494331419245</v>
+        <v>1.13741434866417</v>
       </c>
       <c r="H147" t="n">
-        <v>0.88577020415061</v>
+        <v>0.896491338288336</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B148" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C148" t="s">
         <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E148" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F148" t="n">
-        <v>0.699179681198832</v>
+        <v>0.682766935282337</v>
       </c>
       <c r="G148" t="n">
-        <v>1.12799460199462</v>
+        <v>0.829147013792629</v>
       </c>
       <c r="H148" t="n">
-        <v>0.88577020415061</v>
+        <v>0.896842331702493</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E149" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="F149" t="n">
-        <v>0.719823508255764</v>
+        <v>0.703405750354896</v>
       </c>
       <c r="G149" t="n">
-        <v>0.837021648649028</v>
+        <v>1.10385314529785</v>
       </c>
       <c r="H149" t="n">
-        <v>0.895390217586438</v>
+        <v>0.896842331702493</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
         <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E150" t="n">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="F150" t="n">
-        <v>0.589042267367359</v>
+        <v>0.695484616740845</v>
       </c>
       <c r="G150" t="n">
-        <v>1.24802574892841</v>
+        <v>1.1380145178319</v>
       </c>
       <c r="H150" t="n">
-        <v>0.896491338288336</v>
+        <v>0.896842331702493</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E151" t="n">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="F151" t="n">
-        <v>0.61523915372729</v>
+        <v>0.699179681198832</v>
       </c>
       <c r="G151" t="n">
-        <v>1.33402615134227</v>
+        <v>1.12799460199462</v>
       </c>
       <c r="H151" t="n">
-        <v>0.896491338288336</v>
+        <v>0.896842331702493</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C152" t="s">
         <v>10</v>
       </c>
       <c r="D152" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E152" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F152" t="n">
-        <v>0.60960398069094</v>
+        <v>0.719823508255764</v>
       </c>
       <c r="G152" t="n">
-        <v>0.695857133745228</v>
+        <v>0.837021648649028</v>
       </c>
       <c r="H152" t="n">
-        <v>0.896491338288336</v>
+        <v>0.906444417803554</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C153" t="s">
         <v>10</v>
       </c>
       <c r="D153" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E153" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="F153" t="n">
-        <v>0.615173320702119</v>
+        <v>0.739905876333053</v>
       </c>
       <c r="G153" t="n">
-        <v>1.13741434866417</v>
+        <v>1.11884130194171</v>
       </c>
       <c r="H153" t="n">
-        <v>0.896491338288336</v>
+        <v>0.90942505050934</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C154" t="s">
         <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E154" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="F154" t="n">
-        <v>0.739905876333053</v>
+        <v>0.740022345022306</v>
       </c>
       <c r="G154" t="n">
-        <v>1.11884130194171</v>
+        <v>0.852211314182209</v>
       </c>
       <c r="H154" t="n">
-        <v>0.8985985618128</v>
+        <v>0.90942505050934</v>
       </c>
     </row>
     <row r="155">
@@ -4553,30 +4553,30 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
         <v>10</v>
       </c>
       <c r="D155" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E155" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F155" t="n">
-        <v>0.740022345022306</v>
+        <v>0.752386008643869</v>
       </c>
       <c r="G155" t="n">
-        <v>0.852211314182209</v>
+        <v>1.13924181298246</v>
       </c>
       <c r="H155" t="n">
-        <v>0.8985985618128</v>
+        <v>0.913611581924698</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B156" t="s">
         <v>24</v>
@@ -4585,19 +4585,19 @@
         <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E156" t="n">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="F156" t="n">
-        <v>0.752386008643869</v>
+        <v>0.780964594546653</v>
       </c>
       <c r="G156" t="n">
-        <v>1.13924181298246</v>
+        <v>1.11916834550915</v>
       </c>
       <c r="H156" t="n">
-        <v>0.902863210372642</v>
+        <v>0.934553588600633</v>
       </c>
     </row>
     <row r="157">
